--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -1815,7 +1815,7 @@
         <v>78458216</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317778.0176741602</v>
+        <v>317778</v>
       </c>
       <c r="R11" t="n">
-        <v>6591499.716069377</v>
+        <v>6591500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1894,19 +1894,9 @@
           <t>2019-06-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-06-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4635,7 +4625,7 @@
         <v>81745280</v>
       </c>
       <c r="B34" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4677,10 +4667,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>318282.1920354631</v>
+        <v>318282</v>
       </c>
       <c r="R34" t="n">
-        <v>6591494.248960914</v>
+        <v>6591494</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4710,19 +4700,9 @@
           <t>2019-10-21</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2019-10-21</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -6491,7 +6471,7 @@
         <v>93588017</v>
       </c>
       <c r="B50" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6541,10 +6521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>317342.3377212841</v>
+        <v>317342</v>
       </c>
       <c r="R50" t="n">
-        <v>6591264.411512152</v>
+        <v>6591265</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6574,19 +6554,9 @@
           <t>2021-05-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9288,10 +9288,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>102262757</v>
+        <v>124135731</v>
       </c>
       <c r="B71" t="n">
-        <v>96334</v>
+        <v>91602</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9300,46 +9300,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Söder om Tutjärnen, Vrm</t>
+          <t>Valåsen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317262.6606318104</v>
+        <v>318368</v>
       </c>
       <c r="R71" t="n">
-        <v>6591084.767739117</v>
+        <v>6591598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9366,22 +9365,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9399,6 +9388,21 @@
           <t>Barrblandskog</t>
         </is>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Låga, svampen under # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
@@ -9411,6 +9415,269 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>124136713</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tutjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>317495</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6591361</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Västra Fågelvik</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Barrblandskog, mosskant</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Torrträd # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>102262757</v>
+      </c>
+      <c r="B73" t="n">
+        <v>96334</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Söder om Tutjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>317262.6606318104</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6591084.767739117</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Västra Fågelvik</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9555,10 +9555,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>102262757</v>
+        <v>124166044</v>
       </c>
       <c r="B73" t="n">
-        <v>96334</v>
+        <v>90028</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9567,46 +9567,45 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>58</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Isabellporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia bombycina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Söder om Tutjärnen, Vrm</t>
+          <t>Öster om Tutjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>317262.6606318104</v>
+        <v>317581</v>
       </c>
       <c r="R73" t="n">
-        <v>6591084.767739117</v>
+        <v>6591401</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9633,22 +9632,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9666,6 +9655,21 @@
           <t>Barrblandskog</t>
         </is>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Låga, svampen på undersidan # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
@@ -9678,6 +9682,132 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>102262757</v>
+      </c>
+      <c r="B74" t="n">
+        <v>96334</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Söder om Tutjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>317262.6606318104</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6591084.767739117</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Västra Fågelvik</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -9288,10 +9288,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124135731</v>
+        <v>124136713</v>
       </c>
       <c r="B71" t="n">
-        <v>91602</v>
+        <v>5001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9304,41 +9304,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Valåsen, Vrm</t>
+          <t>Tutjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>318368</v>
+        <v>317495</v>
       </c>
       <c r="R71" t="n">
-        <v>6591598</v>
+        <v>6591361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9373,6 +9375,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9385,22 +9392,22 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga, svampen under # Pinus sylvestris</t>
+          <t>Torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9418,10 +9425,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124136713</v>
+        <v>124135731</v>
       </c>
       <c r="B72" t="n">
-        <v>5001</v>
+        <v>91602</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9434,43 +9441,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105212</v>
+        <v>5454</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tutjärnen, Vrm</t>
+          <t>Valåsen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317495</v>
+        <v>318368</v>
       </c>
       <c r="R72" t="n">
-        <v>6591361</v>
+        <v>6591598</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9505,11 +9510,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9522,22 +9522,22 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Torrträd # Picea abies</t>
+          <t>Låga, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -9288,10 +9288,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124136713</v>
+        <v>124135731</v>
       </c>
       <c r="B71" t="n">
-        <v>5001</v>
+        <v>91624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9304,43 +9304,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105212</v>
+        <v>5454</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tutjärnen, Vrm</t>
+          <t>Valåsen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>317495</v>
+        <v>318368</v>
       </c>
       <c r="R71" t="n">
-        <v>6591361</v>
+        <v>6591598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9375,11 +9373,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9392,22 +9385,22 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Torrträd # Picea abies</t>
+          <t>Låga, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9425,10 +9418,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124135731</v>
+        <v>124136713</v>
       </c>
       <c r="B72" t="n">
-        <v>91624</v>
+        <v>5001</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9441,41 +9434,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Valåsen, Vrm</t>
+          <t>Tutjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>318368</v>
+        <v>317495</v>
       </c>
       <c r="R72" t="n">
-        <v>6591598</v>
+        <v>6591361</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9510,6 +9505,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9522,22 +9522,22 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Låga, svampen under # Pinus sylvestris</t>
+          <t>Torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 25557-2019 artfynd.xlsx
+++ b/artfynd/A 25557-2019 artfynd.xlsx
@@ -9288,10 +9288,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124135731</v>
+        <v>124136713</v>
       </c>
       <c r="B71" t="n">
-        <v>91624</v>
+        <v>5001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9304,41 +9304,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5454</v>
+        <v>105212</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Barrpraktbagge</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Chrysobothris chrysostigma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Valåsen, Vrm</t>
+          <t>Tutjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>318368</v>
+        <v>317495</v>
       </c>
       <c r="R71" t="n">
-        <v>6591598</v>
+        <v>6591361</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9373,6 +9375,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -9385,22 +9392,22 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog, mosskant</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Låga, svampen under # Pinus sylvestris</t>
+          <t>Torrträd # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9418,10 +9425,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124136713</v>
+        <v>124135731</v>
       </c>
       <c r="B72" t="n">
-        <v>5001</v>
+        <v>91624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9434,43 +9441,41 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105212</v>
+        <v>5454</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tutjärnen, Vrm</t>
+          <t>Valåsen, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>317495</v>
+        <v>318368</v>
       </c>
       <c r="R72" t="n">
-        <v>6591361</v>
+        <v>6591598</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9505,11 +9510,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Gnag til hälften i bark/ved, hål 5 mm, nedgång 3 cm, ganska parallelt med fiber.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9522,22 +9522,22 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Barrblandskog, mosskant</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Torrträd # Picea abies</t>
+          <t>Låga, svampen under # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
